--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2682,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN_MARTIN</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>0019</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.4937</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.37050000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>501</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.4937</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.3705</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>0750 ELSA PEREA FLORES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.50369</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.36725</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1169</v>
-      </c>
-      <c r="J3" t="n">
-        <v>51</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.50369</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.36725</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>168</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.49667</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.36302000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>235</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.49667</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.36302</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>301</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.48474</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.357748</v>
-      </c>
-      <c r="I5" t="n">
-        <v>254</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.48474</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.357748</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>315</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.484482</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.36273799999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>277</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.484482</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.362738</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>326 MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.48024</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.36975</v>
-      </c>
-      <c r="I7" t="n">
-        <v>415</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.48024</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.36975</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>327</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.481535</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.359225</v>
-      </c>
-      <c r="I8" t="n">
-        <v>212</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.481535</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.359225</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>330</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.486097</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.373857</v>
-      </c>
-      <c r="I9" t="n">
-        <v>261</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.486097</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.373857</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>TARAPOTO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.478565</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.36854</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1210</v>
-      </c>
-      <c r="J10" t="n">
-        <v>53</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.478565</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.36854</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>0004 / 0004 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.49085</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.37566</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1158</v>
-      </c>
-      <c r="J11" t="n">
-        <v>52</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.49085</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.37566</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0017 JULIO MARIO RUIZ ZAMORA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.4936</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.3629</v>
-      </c>
-      <c r="I12" t="n">
-        <v>563</v>
-      </c>
-      <c r="J12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.4936</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.3629</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>0018 FLOR DE BELEN TUESTA REATEGUI</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.486232</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.362239</v>
-      </c>
-      <c r="I13" t="n">
-        <v>786</v>
-      </c>
-      <c r="J13" t="n">
-        <v>33</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.486232</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.362239</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>0026</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.5248</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.3796</v>
-      </c>
-      <c r="I14" t="n">
-        <v>307</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.5248</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.3796</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>0106</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.494098</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.381472</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1055</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.494098</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.381472</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>0528</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.500124</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.378361</v>
-      </c>
-      <c r="I16" t="n">
-        <v>508</v>
-      </c>
-      <c r="J16" t="n">
-        <v>23</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.500124</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.378361</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>0556</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-6.487081</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.35521199999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>362</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.487081</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.355212</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>0620 APLICACION</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-6.49012</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.366</v>
-      </c>
-      <c r="I18" t="n">
-        <v>789</v>
-      </c>
-      <c r="J18" t="n">
-        <v>31</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.49012</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.366</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>0705 JUANITA DEL CARMEN SANCHEZ ROJAS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-6.48055</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.36973999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>600</v>
-      </c>
-      <c r="J19" t="n">
-        <v>32</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-6.48055</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.36974</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>JUAN MIGUEL PEREZ RENGIFO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-6.477222</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.360604</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1111</v>
-      </c>
-      <c r="J20" t="n">
-        <v>51</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-6.477222</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.360604</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>JOSE ANTONIO RAMIREZ AREVALO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-6.4893</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.35939999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>568</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-6.4893</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.3594</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>MIGUEL CHUQUISENGO RAMIREZ</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-6.4951</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.369</v>
-      </c>
-      <c r="I22" t="n">
-        <v>445</v>
-      </c>
-      <c r="J22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-6.4951</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.369</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>ANGEL CUSTODIO GARCIA RAMIREZ</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-6.487091</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.373597</v>
-      </c>
-      <c r="I23" t="n">
-        <v>914</v>
-      </c>
-      <c r="J23" t="n">
-        <v>42</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.487091</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.373597</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>0655 JOSE E. CELIS BARDALES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-6.486687</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.363799</v>
-      </c>
-      <c r="I24" t="n">
-        <v>923</v>
-      </c>
-      <c r="J24" t="n">
-        <v>37</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-6.486687</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.363799</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-6.48855</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.36729</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1478</v>
-      </c>
-      <c r="J25" t="n">
-        <v>71</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-6.48855</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.36729</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>OFELIA VELASQUEZ</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-6.4868</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.36190000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1224</v>
-      </c>
-      <c r="J26" t="n">
-        <v>58</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-6.4868</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.3619</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-6.49116</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.36360000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1479</v>
-      </c>
-      <c r="J27" t="n">
-        <v>65</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-6.49116</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.3636</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-6.48575</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.35887200000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>222</v>
-      </c>
-      <c r="J28" t="n">
-        <v>10</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-6.48575</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.358872</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-6.48077</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.3687</v>
-      </c>
-      <c r="I29" t="n">
-        <v>241</v>
-      </c>
-      <c r="J29" t="n">
-        <v>16</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-6.48077</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.3687</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-6.48647</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.35467</v>
-      </c>
-      <c r="I30" t="n">
-        <v>302</v>
-      </c>
-      <c r="J30" t="n">
-        <v>21</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-6.48647</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.35467</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>CRISTINA GARCIA BLANCO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-6.483904</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.35961399999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>351</v>
-      </c>
-      <c r="J31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-6.483904</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.359614</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>0049 ANTONIO RAIMONDI</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-6.4634</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.4495</v>
-      </c>
-      <c r="I32" t="n">
-        <v>380</v>
-      </c>
-      <c r="J32" t="n">
-        <v>19</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-6.4634</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.4495</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>0663 PABLO CHAVEZ VILLAVERDE</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-6.69067</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.21908000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1135</v>
-      </c>
-      <c r="J33" t="n">
-        <v>54</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-6.69067</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.21908</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>APLICACION ISPP - TARAPOTO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-6.490043</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.36539500000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>410</v>
-      </c>
-      <c r="J34" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-6.490043</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.365395</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-6.46481</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.448048</v>
-      </c>
-      <c r="I35" t="n">
-        <v>479</v>
-      </c>
-      <c r="J35" t="n">
-        <v>34</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-6.46481</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.448048</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>CIENCIAS</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-6.47955</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.36244000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>830</v>
-      </c>
-      <c r="J36" t="n">
-        <v>46</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-6.47955</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.36244</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-6.48647</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.35467</v>
-      </c>
-      <c r="I37" t="n">
-        <v>428</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-6.48647</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.35467</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-6.48684</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.35472</v>
-      </c>
-      <c r="I38" t="n">
-        <v>229</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-6.48684</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.35472</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-6.47568</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.37260000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>11</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6.47568</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.3726</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-6.496247</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.368679</v>
-      </c>
-      <c r="I40" t="n">
-        <v>570</v>
-      </c>
-      <c r="J40" t="n">
-        <v>50</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-6.496247</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.368679</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN LUCAS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-6.481598</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.360381</v>
-      </c>
-      <c r="I41" t="n">
-        <v>419</v>
-      </c>
-      <c r="J41" t="n">
-        <v>34</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-6.481598</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.360381</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-6.488963</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.367154</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1381</v>
-      </c>
-      <c r="J42" t="n">
-        <v>54</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-6.488963</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.367154</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>VALORES Y CIENCIAS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-6.48986</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.37026</v>
-      </c>
-      <c r="I43" t="n">
-        <v>338</v>
-      </c>
-      <c r="J43" t="n">
-        <v>22</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-6.48986</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.37026</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-6.47491</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.37087</v>
-      </c>
-      <c r="I44" t="n">
-        <v>390</v>
-      </c>
-      <c r="J44" t="n">
-        <v>26</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-6.47491</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.37087</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>481589</t>
+          <t>481688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.4937</t>
+          <t>-6.481535</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.3705</t>
+          <t>-76.359225</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>481607</t>
+          <t>481971</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0750 ELSA PEREA FLORES</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.50369</t>
+          <t>-6.48575</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.36725</t>
+          <t>-76.358872</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>481626</t>
+          <t>481645</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.49667</t>
+          <t>-6.48474</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.36302</t>
+          <t>-76.357748</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>481645</t>
+          <t>481650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.48474</t>
+          <t>-6.484482</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.357748</t>
+          <t>-76.362738</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>481650</t>
+          <t>481693</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.484482</t>
+          <t>-6.486097</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.362738</t>
+          <t>-76.373857</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>481674</t>
+          <t>510879</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>326 MI DIVINO NIÑO JESUS</t>
+          <t>APLICACION ISPP - TARAPOTO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.48024</t>
+          <t>-6.490043</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.36975</t>
+          <t>-76.365395</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>481688</t>
+          <t>481749</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>0026</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.481535</t>
+          <t>-6.5248</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.359225</t>
+          <t>-76.3796</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>481693</t>
+          <t>481985</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.486097</t>
+          <t>-6.48077</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.373857</t>
+          <t>-76.3687</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>481706</t>
+          <t>715828</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TARAPOTO</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.478565</t>
+          <t>-6.48684</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.36854</t>
+          <t>-76.35472</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>481711</t>
+          <t>481674</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0004 / 0004 TUPAC AMARU</t>
+          <t>326 MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.49085</t>
+          <t>-6.48024</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.37566</t>
+          <t>-76.36975</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>481725</t>
+          <t>482249</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0017 JULIO MARIO RUIZ ZAMORA</t>
+          <t>0049 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.4936</t>
+          <t>-6.4634</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.3629</t>
+          <t>-76.4495</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>380</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>481730</t>
+          <t>781922</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0018 FLOR DE BELEN TUESTA REATEGUI</t>
+          <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.486232</t>
+          <t>-6.47568</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.362239</t>
+          <t>-76.3726</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>481749</t>
+          <t>481792</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0026</t>
+          <t>0556</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.5248</t>
+          <t>-6.487081</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.3796</t>
+          <t>-76.355212</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>481754</t>
+          <t>482027</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0106</t>
+          <t>CRISTINA GARCIA BLANCO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.494098</t>
+          <t>-6.483904</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.381472</t>
+          <t>-76.359614</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>481773</t>
+          <t>482008</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0528</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.500124</t>
+          <t>-6.48647</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.378361</t>
+          <t>-76.35467</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>302</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>481792</t>
+          <t>481853</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0556</t>
+          <t>MIGUEL CHUQUISENGO RAMIREZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.487081</t>
+          <t>-6.4951</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.355212</t>
+          <t>-76.369</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>445</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>481805</t>
+          <t>823366</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0620 APLICACION</t>
+          <t>VALORES Y CIENCIAS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.49012</t>
+          <t>-6.48986</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.366</t>
+          <t>-76.37026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>481829</t>
+          <t>481773</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0705 JUANITA DEL CARMEN SANCHEZ ROJAS</t>
+          <t>0528</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.48055</t>
+          <t>-6.500124</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.36974</t>
+          <t>-76.378361</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>508</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>481834</t>
+          <t>481589</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JUAN MIGUEL PEREZ RENGIFO</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.477222</t>
+          <t>-6.4937</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.360604</t>
+          <t>-76.3705</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>501</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>481848</t>
+          <t>649089</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO RAMIREZ AREVALO</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.4893</t>
+          <t>-6.48647</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.3594</t>
+          <t>-76.35467</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>481725</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MIGUEL CHUQUISENGO RAMIREZ</t>
+          <t>0017 JULIO MARIO RUIZ ZAMORA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.4951</t>
+          <t>-6.4936</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.369</t>
+          <t>-76.3629</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>563</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>481867</t>
+          <t>910113</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANGEL CUSTODIO GARCIA RAMIREZ</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.487091</t>
+          <t>-6.47491</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.373597</t>
+          <t>-76.37087</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>481872</t>
+          <t>481848</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0655 JOSE E. CELIS BARDALES</t>
+          <t>JOSE ANTONIO RAMIREZ AREVALO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.486687</t>
+          <t>-6.4893</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.363799</t>
+          <t>-76.3594</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>568</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>481886</t>
+          <t>481805</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JUAN JIMENEZ PIMENTEL</t>
+          <t>0620 APLICACION</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.48855</t>
+          <t>-6.49012</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.36729</t>
+          <t>-76.366</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>789</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>481891</t>
+          <t>481829</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OFELIA VELASQUEZ</t>
+          <t>0705 JUANITA DEL CARMEN SANCHEZ ROJAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.4868</t>
+          <t>-6.48055</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.3619</t>
+          <t>-76.36974</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>481909</t>
+          <t>481730</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>0018 FLOR DE BELEN TUESTA REATEGUI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.49116</t>
+          <t>-6.486232</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.3636</t>
+          <t>-76.362239</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>786</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>481971</t>
+          <t>548679</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.48575</t>
+          <t>-6.46481</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.358872</t>
+          <t>-76.448048</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>479</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>481985</t>
+          <t>801736</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>SAN LUCAS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.48077</t>
+          <t>-6.481598</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.3687</t>
+          <t>-76.360381</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>482008</t>
+          <t>481872</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>0655 JOSE E. CELIS BARDALES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.48647</t>
+          <t>-6.486687</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.35467</t>
+          <t>-76.363799</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>923</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>482027</t>
+          <t>481867</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CRISTINA GARCIA BLANCO</t>
+          <t>ANGEL CUSTODIO GARCIA RAMIREZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.483904</t>
+          <t>-6.487091</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.359614</t>
+          <t>-76.373597</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>914</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>482249</t>
+          <t>481754</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0049 ANTONIO RAIMONDI</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.4634</t>
+          <t>-6.494098</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.4495</t>
+          <t>-76.381472</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>483828</t>
+          <t>553661</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0663 PABLO CHAVEZ VILLAVERDE</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.69067</t>
+          <t>-6.47955</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.21908</t>
+          <t>-76.36244</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>830</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>510879</t>
+          <t>801703</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>APLICACION ISPP - TARAPOTO</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.490043</t>
+          <t>-6.496247</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.365395</t>
+          <t>-76.368679</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>570</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>548679</t>
+          <t>481607</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>0750 ELSA PEREA FLORES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.46481</t>
+          <t>-6.50369</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.448048</t>
+          <t>-76.36725</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>553661</t>
+          <t>481834</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>JUAN MIGUEL PEREZ RENGIFO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.47955</t>
+          <t>-6.477222</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.36244</t>
+          <t>-76.360604</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>649089</t>
+          <t>481711</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>0004 / 0004 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-6.48647</t>
+          <t>-6.49085</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.35467</t>
+          <t>-76.37566</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>715828</t>
+          <t>481706</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>TARAPOTO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.48684</t>
+          <t>-6.478565</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.35472</t>
+          <t>-76.36854</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>781922</t>
+          <t>483828</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ALEXANDER GRAHAM BELL</t>
+          <t>0663 PABLO CHAVEZ VILLAVERDE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.47568</t>
+          <t>-6.69067</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.3726</t>
+          <t>-76.21908</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>801703</t>
+          <t>801779</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.496247</t>
+          <t>-6.488963</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.368679</t>
+          <t>-76.367154</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>801736</t>
+          <t>481891</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN LUCAS</t>
+          <t>OFELIA VELASQUEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.481598</t>
+          <t>-6.4868</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.360381</t>
+          <t>-76.3619</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>801779</t>
+          <t>481909</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JUAN JIMENEZ PIMENTEL</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.488963</t>
+          <t>-6.49116</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.367154</t>
+          <t>-76.3636</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>823366</t>
+          <t>481886</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VALORES Y CIENCIAS</t>
+          <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.48986</t>
+          <t>-6.48855</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.37026</t>
+          <t>-76.36729</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>910113</t>
+          <t>481626</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.47491</t>
+          <t>-6.49667</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.37087</t>
+          <t>-76.36302</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>481688</t>
+          <t>910113</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.481535</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.359225</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-6.47491</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.37087</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>481971</t>
+          <t>823366</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MI PEQUEÑO MUNDO</t>
+          <t>VALORES Y CIENCIAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.48575</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.358872</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-6.48986</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.37026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>481645</t>
+          <t>801779</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.48474</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.357748</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-6.488963</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.367154</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>481650</t>
+          <t>801736</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>SAN LUCAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.484482</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.362738</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-6.481598</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.360381</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>481693</t>
+          <t>801703</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.486097</t>
+          <t>570</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.373857</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-6.496247</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.368679</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>510879</t>
+          <t>781922</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APLICACION ISPP - TARAPOTO</t>
+          <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.490043</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.365395</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-6.47568</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.3726</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>481749</t>
+          <t>715828</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0026</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.5248</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.3796</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-6.48684</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.35472</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>481985</t>
+          <t>649089</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.48077</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.3687</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-6.48647</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.35467</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>715828</t>
+          <t>553661</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.48684</t>
+          <t>830</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.35472</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-6.47955</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.36244</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>481674</t>
+          <t>548679</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>326 MI DIVINO NIÑO JESUS</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.48024</t>
+          <t>479</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.36975</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-6.46481</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.448048</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>482249</t>
+          <t>510879</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0049 ANTONIO RAIMONDI</t>
+          <t>APLICACION ISPP - TARAPOTO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.4634</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-76.4495</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>-6.490043</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-76.365395</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>781922</t>
+          <t>483828</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ALEXANDER GRAHAM BELL</t>
+          <t>0663 PABLO CHAVEZ VILLAVERDE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.47568</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.3726</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-6.69067</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.21908</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>481792</t>
+          <t>482249</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0556</t>
+          <t>0049 ANTONIO RAIMONDI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.487081</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.355212</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-6.4634</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-76.4495</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>-6.483904</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>-76.359614</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-6.48647</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-76.35467</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>481985</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MIGUEL CHUQUISENGO RAMIREZ</t>
+          <t>JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.4951</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.369</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>-6.48077</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.3687</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>823366</t>
+          <t>481971</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VALORES Y CIENCIAS</t>
+          <t>MI PEQUEÑO MUNDO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.48986</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.37026</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-6.48575</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-76.358872</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>481773</t>
+          <t>481909</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0528</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.500124</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.378361</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>-6.49116</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.3636</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>481589</t>
+          <t>481891</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0019</t>
+          <t>OFELIA VELASQUEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.4937</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.3705</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>-6.4868</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.3619</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>649089</t>
+          <t>481886</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SIMON BOLIVAR</t>
+          <t>JUAN JIMENEZ PIMENTEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.48647</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.35467</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-6.48855</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.36729</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>481725</t>
+          <t>481872</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0017 JULIO MARIO RUIZ ZAMORA</t>
+          <t>0655 JOSE E. CELIS BARDALES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-6.4936</t>
+          <t>923</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.3629</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>-6.486687</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-76.363799</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>910113</t>
+          <t>481867</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JOSE DE SAN MARTIN</t>
+          <t>ANGEL CUSTODIO GARCIA RAMIREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.47491</t>
+          <t>914</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.37087</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-6.487091</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.373597</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>481848</t>
+          <t>481853</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO RAMIREZ AREVALO</t>
+          <t>MIGUEL CHUQUISENGO RAMIREZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-6.4893</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.3594</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>-6.4951</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.369</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>481805</t>
+          <t>481848</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0620 APLICACION</t>
+          <t>JOSE ANTONIO RAMIREZ AREVALO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.49012</t>
+          <t>568</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.366</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>-6.4893</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-76.3594</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>481829</t>
+          <t>481834</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0705 JUANITA DEL CARMEN SANCHEZ ROJAS</t>
+          <t>JUAN MIGUEL PEREZ RENGIFO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.48055</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.36974</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>-6.477222</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.360604</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>481730</t>
+          <t>481829</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0018 FLOR DE BELEN TUESTA REATEGUI</t>
+          <t>0705 JUANITA DEL CARMEN SANCHEZ ROJAS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-6.486232</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.362239</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>-6.48055</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.36974</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>548679</t>
+          <t>481805</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>0620 APLICACION</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.46481</t>
+          <t>789</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.448048</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>-6.49012</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.366</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>801736</t>
+          <t>481792</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SAN LUCAS</t>
+          <t>0556</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-6.481598</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.360381</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-6.487081</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.355212</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>481872</t>
+          <t>481773</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0655 JOSE E. CELIS BARDALES</t>
+          <t>0528</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.486687</t>
+          <t>508</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.363799</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>-6.500124</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-76.378361</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>481867</t>
+          <t>481754</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANGEL CUSTODIO GARCIA RAMIREZ</t>
+          <t>0106</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.487091</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.373597</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>-6.494098</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-76.381472</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>481754</t>
+          <t>481749</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0106</t>
+          <t>0026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-6.494098</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.381472</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>-6.5248</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.3796</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>553661</t>
+          <t>481730</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>0018 FLOR DE BELEN TUESTA REATEGUI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-6.47955</t>
+          <t>786</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.36244</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>-6.486232</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.362239</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>801703</t>
+          <t>481725</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>0017 JULIO MARIO RUIZ ZAMORA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.496247</t>
+          <t>563</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.368679</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>-6.4936</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-76.3629</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>481607</t>
+          <t>481711</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0750 ELSA PEREA FLORES</t>
+          <t>0004 / 0004 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.50369</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.36725</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>-6.49085</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.37566</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>481834</t>
+          <t>481706</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JUAN MIGUEL PEREZ RENGIFO</t>
+          <t>TARAPOTO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.477222</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.360604</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>-6.478565</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.36854</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>481711</t>
+          <t>481693</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0004 / 0004 TUPAC AMARU</t>
+          <t>330</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-6.49085</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.37566</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>-6.486097</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.373857</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>481706</t>
+          <t>481688</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TARAPOTO</t>
+          <t>327</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.478565</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.36854</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>-6.481535</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-76.359225</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>483828</t>
+          <t>481674</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0663 PABLO CHAVEZ VILLAVERDE</t>
+          <t>326 MI DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-6.69067</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.21908</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>-6.48024</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-76.36975</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>801779</t>
+          <t>481650</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JUAN JIMENEZ PIMENTEL</t>
+          <t>315</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.488963</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.367154</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>-6.484482</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-76.362738</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>481891</t>
+          <t>481645</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OFELIA VELASQUEZ</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.4868</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.3619</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>-6.48474</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-76.357748</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>481909</t>
+          <t>481626</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.49116</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.3636</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>-6.49667</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-76.36302</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>481886</t>
+          <t>481607</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JUAN JIMENEZ PIMENTEL</t>
+          <t>0750 ELSA PEREA FLORES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.48855</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.36729</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>-6.50369</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-76.36725</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>481626</t>
+          <t>481589</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>0019</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-6.49667</t>
+          <t>501</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.36302</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-6.4937</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-76.3705</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">

--- a/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
+++ b/ZonasEscolares/excels/SAN_MARTIN-SAN_MARTIN-TARAPOTO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
